--- a/stories/arbres/TREE-AUT-028.xlsx
+++ b/stories/arbres/TREE-AUT-028.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Sami est avec maman, dans la chambre. Sami a envie de jouer. maman est là, tout près. On va apprendre : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami écoute maman. Sami entend les mots : reprendre ses affaires, avant de partir.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1513,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1542,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers le bac à sable. La couverture est douce. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On souffle doucement. maman dit : je suis là. On reste ensemble.</t>
+          <t>Sami va vers le bac à sable. La couverture est douce. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1680,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sami va vers le bac à sable. La couverture est douce. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On souffle doucement.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1866,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2039,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sami respire. Sami retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2187,6 +2230,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2349,6 +2397,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le ballon. Ça sent le pain chaud. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2537,6 +2590,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2701,6 +2759,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2863,6 +2926,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3025,6 +3093,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3187,6 +3260,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3349,6 +3427,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3511,6 +3594,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3673,6 +3761,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le seau. Le vent est doux. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3861,6 +3954,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4025,6 +4123,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4187,6 +4290,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4349,6 +4457,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4511,6 +4624,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4673,6 +4791,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. La lumière est claire. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4835,6 +4958,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4997,6 +5125,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le doudou. Le sol est un peu froid. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5185,6 +5318,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5349,6 +5487,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5511,6 +5654,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5673,6 +5821,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5835,6 +5988,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5997,6 +6155,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6159,6 +6322,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6183,7 +6351,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers le toboggan. On entend un oiseau. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On écoute jusqu'au bout. maman dit : je suis là. On reste ensemble.</t>
+          <t>Sami va vers le toboggan. On entend un oiseau. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6321,6 +6489,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Sami va vers le toboggan. On entend un oiseau. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On écoute jusqu'au bout.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6501,6 +6675,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
     </row>
@@ -6669,6 +6848,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sami respire. Sami retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6855,6 +7039,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7017,6 +7206,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le ballon. Une feuille tombe. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7205,6 +7399,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7369,6 +7568,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7531,6 +7735,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7693,6 +7902,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7855,6 +8069,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8017,6 +8236,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8179,6 +8403,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8341,6 +8570,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le seau. L'eau coule, tout petit bruit. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8529,6 +8763,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8693,6 +8932,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8855,6 +9099,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9017,6 +9266,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. La lumière est claire. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9179,6 +9433,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9341,6 +9600,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9503,6 +9767,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9665,6 +9934,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le doudou. Un vélo passe au loin. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9853,6 +10127,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10017,6 +10296,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10179,6 +10463,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10341,6 +10630,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10503,6 +10797,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10665,6 +10964,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10827,6 +11131,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10851,7 +11160,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers les balançoires. Ça sent le pain chaud. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On attend son tour. maman dit : je suis là. On reste ensemble.</t>
+          <t>Sami va vers les balançoires. Ça sent le pain chaud. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On attend son tour. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10989,6 +11298,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sami va vers les balançoires. Ça sent le pain chaud. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On attend son tour.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11169,6 +11484,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
     </row>
@@ -11337,6 +11657,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sami respire. Sami retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11523,6 +11848,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11685,6 +12015,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le ballon. La lumière est claire. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11873,6 +12208,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12037,6 +12377,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12199,6 +12544,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12361,6 +12711,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12523,6 +12878,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12685,6 +13045,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12847,6 +13212,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13009,6 +13379,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le seau. Il y a des miettes sur la table. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13197,6 +13572,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13361,6 +13741,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. La lumière est claire. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13523,6 +13908,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13685,6 +14075,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13847,6 +14242,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14009,6 +14409,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14171,6 +14576,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14333,6 +14743,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le doudou. Un chat miaule une fois. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14521,6 +14936,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14685,6 +15105,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14847,6 +15272,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15009,6 +15439,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15171,6 +15606,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15333,6 +15773,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15495,6 +15940,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15513,7 +15963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15586,6 +16036,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-028.xlsx
+++ b/stories/arbres/TREE-AUT-028.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Sami est avec maman, dans la chambre. Sami a envie de jouer. maman est là, tout près. On va apprendre : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami écoute maman. Sami entend les mots : reprendre ses affaires, avant de partir.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1686,6 +1693,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1873,6 +1881,7 @@
           <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2044,6 +2053,7 @@
           <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sami respire. Sami retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2235,6 +2245,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2402,6 +2413,7 @@
           <t>narrateur|Sami a choisi le ballon. Ça sent le pain chaud. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2597,6 +2609,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2764,6 +2777,7 @@
           <t>narrateur|Sami rejoint Tom. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2931,6 +2945,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3098,6 +3113,7 @@
           <t>narrateur|Sami rejoint Léa. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3265,6 +3281,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3432,6 +3449,7 @@
           <t>narrateur|Sami rejoint Sami. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3599,6 +3617,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3766,6 +3785,7 @@
           <t>narrateur|Sami a choisi le seau. Le vent est doux. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3961,6 +3981,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4128,6 +4149,7 @@
           <t>narrateur|Sami rejoint Tom. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4295,6 +4317,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4462,6 +4485,7 @@
           <t>narrateur|Sami rejoint Léa. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4629,6 +4653,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4796,6 +4821,7 @@
           <t>narrateur|Sami rejoint Sami. La lumière est claire. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4963,6 +4989,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5130,6 +5157,7 @@
           <t>narrateur|Sami a choisi le doudou. Le sol est un peu froid. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5325,6 +5353,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5492,6 +5521,7 @@
           <t>narrateur|Sami rejoint Tom. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5659,6 +5689,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5826,6 +5857,7 @@
           <t>narrateur|Sami rejoint Léa. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5993,6 +6025,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6160,6 +6193,7 @@
           <t>narrateur|Sami rejoint Sami. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6327,6 +6361,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6495,6 +6530,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6682,6 +6718,7 @@
           <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6853,6 +6890,7 @@
           <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sami respire. Sami retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7044,6 +7082,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7211,6 +7250,7 @@
           <t>narrateur|Sami a choisi le ballon. Une feuille tombe. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7406,6 +7446,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7573,6 +7614,7 @@
           <t>narrateur|Sami rejoint Tom. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7740,6 +7782,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7907,6 +7950,7 @@
           <t>narrateur|Sami rejoint Léa. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8074,6 +8118,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8241,6 +8286,7 @@
           <t>narrateur|Sami rejoint Sami. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8408,6 +8454,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8575,6 +8622,7 @@
           <t>narrateur|Sami a choisi le seau. L'eau coule, tout petit bruit. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8770,6 +8818,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8937,6 +8986,7 @@
           <t>narrateur|Sami rejoint Tom. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9104,6 +9154,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9271,6 +9322,7 @@
           <t>narrateur|Sami rejoint Léa. La lumière est claire. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9438,6 +9490,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9605,6 +9658,7 @@
           <t>narrateur|Sami rejoint Sami. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9772,6 +9826,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9939,6 +9994,7 @@
           <t>narrateur|Sami a choisi le doudou. Un vélo passe au loin. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10134,6 +10190,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10301,6 +10358,7 @@
           <t>narrateur|Sami rejoint Tom. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10468,6 +10526,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10635,6 +10694,7 @@
           <t>narrateur|Sami rejoint Léa. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10802,6 +10862,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10969,6 +11030,7 @@
           <t>narrateur|Sami rejoint Sami. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11136,6 +11198,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11304,6 +11367,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11491,6 +11555,7 @@
           <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11662,6 +11727,7 @@
           <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sami respire. Sami retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11853,6 +11919,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12020,6 +12087,7 @@
           <t>narrateur|Sami a choisi le ballon. La lumière est claire. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12215,6 +12283,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12382,6 +12451,7 @@
           <t>narrateur|Sami rejoint Tom. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12549,6 +12619,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12716,6 +12787,7 @@
           <t>narrateur|Sami rejoint Léa. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12883,6 +12955,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13050,6 +13123,7 @@
           <t>narrateur|Sami rejoint Sami. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13217,6 +13291,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13384,6 +13459,7 @@
           <t>narrateur|Sami a choisi le seau. Il y a des miettes sur la table. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13579,6 +13655,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13746,6 +13823,7 @@
           <t>narrateur|Sami rejoint Tom. La lumière est claire. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13913,6 +13991,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14080,6 +14159,7 @@
           <t>narrateur|Sami rejoint Léa. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14247,6 +14327,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14414,6 +14495,7 @@
           <t>narrateur|Sami rejoint Sami. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14581,6 +14663,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14748,6 +14831,7 @@
           <t>narrateur|Sami a choisi le doudou. Un chat miaule une fois. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14943,6 +15027,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15110,6 +15195,7 @@
           <t>narrateur|Sami rejoint Tom. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15277,6 +15363,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15444,6 +15531,7 @@
           <t>narrateur|Sami rejoint Léa. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15611,6 +15699,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15778,6 +15867,7 @@
           <t>narrateur|Sami rejoint Sami. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15945,6 +16035,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15963,7 +16054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16043,6 +16134,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16057,7 +16162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16244,6 +16349,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-AUT-028.xlsx
+++ b/stories/arbres/TREE-AUT-028.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Retrouver ses affaires avant de partir — dans la chambre</t>
+          <t>Le seau vert de Victorino</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un grain de sable brille sur le rebord. Victorino joue au parc. Avant de partir, il reprend ses affaires.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Sami est avec maman, dans la chambre. Sami a envie de jouer. maman est là, tout près. On va apprendre : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami écoute maman. Sami entend les mots : reprendre ses affaires, avant de partir.</t>
+          <t>Un grain de sable brille sur le rebord. La fenêtre de la chambre est entrouverte. L'air sent l'herbe chaude, tout doux. Au loin, une chaîne de balançoire tinte. Ting, ting. Le doudou de Victorino est assis sur l'oreiller. Il a une oreille un peu pliée. Sous le lit, un seau vert dépasse. Le seau a du sable au fond. Papa plie un manteau gris, tout lentement. Le manteau est encore un peu chaud. Le manteau est prêt, Victorino. Maman souffle sur le grain de sable. Tu as vu le parc, par la fenêtre ? Oui, maman. Le toboggan brille. En ce moment, Victorino enfile une chaussette. On va au parc ! D'accord. On joue. Puis on va reprendre ses affaires. Avant de partir. Victorino pose le pied par terre. Le plancher est tiède.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,10 +1337,37 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Sami est avec maman, dans la chambre. Sami a envie de jouer. maman est là, tout près. On va apprendre : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami écoute maman. Sami entend les mots : reprendre ses affaires, avant de partir.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Un grain de sable brille sur le rebord.
+narrateur|La fenêtre de la chambre est entrouverte.
+narrateur|L'air sent l'herbe chaude, tout doux.
+narrateur|Au loin, une chaîne de balançoire tinte.
+narrateur|Ting, ting.
+narrateur|Le doudou de Victorino est assis sur l'oreiller.
+narrateur|Il a une oreille un peu pliée.
+narrateur|Sous le lit, un seau vert dépasse.
+narrateur|Le seau a du sable au fond.
+narrateur|Papa plie un manteau gris, tout lentement.
+narrateur|Le manteau est encore un peu chaud.
+papa|Le manteau est prêt, Victorino.
+narrateur|Maman souffle sur le grain de sable.
+maman|Tu as vu le parc, par la fenêtre ?
+enfant-m|Oui, maman.
+enfant-m|Le toboggan brille.
+narrateur|En ce moment, Victorino enfile une chaussette.
+enfant-m|On va au parc !
+papa|D'accord.
+papa|On joue.
+maman|Puis on va reprendre ses affaires.
+maman|Avant de partir.
+narrateur|Victorino pose le pied par terre.
+narrateur|Le plancher est tiède.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1353,7 +1392,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>On peut aller au bac à sable, au toboggan, ou aux balançoires.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1521,7 +1560,7 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>narrateur|On peut aller au bac à sable, au toboggan, ou aux balançoires.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1549,7 +1588,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers le bac à sable. La couverture est douce. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On souffle doucement. Je suis là. On reste ensemble.</t>
+          <t>Victorino va vers le bac à sable. Le sable est frais, un peu lourd. Ça fait chh, quand il verse. Ça fait chh, tu as entendu ? Oui. Le sable chante. Le seau vert se remplit. Puis il se vide. Le manteau gris est sur le banc. Le doudou aussi. On joue. Après, on reprend ses affaires. Avant de partir. Seau. Manteau. Doudou. Oui. On les cherche. On les prend. Victorino enfonce les mains. Le sable est froid au fond.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1689,11 +1728,34 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sami va vers le bac à sable. La couverture est douce. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On souffle doucement.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Victorino va vers le bac à sable.
+narrateur|Le sable est frais, un peu lourd.
+narrateur|Ça fait chh, quand il verse.
+papa|Ça fait chh, tu as entendu ?
+enfant-m|Oui.
+enfant-m|Le sable chante.
+narrateur|Le seau vert se remplit.
+narrateur|Puis il se vide.
+maman|Le manteau gris est sur le banc.
+maman|Le doudou aussi.
+papa|On joue.
+papa|Après, on reprend ses affaires.
+papa|Avant de partir.
+enfant-m|Seau.
+enfant-m|Manteau.
+enfant-m|Doudou.
+maman|Oui.
+maman|On les cherche.
+maman|On les prend.
+narrateur|Victorino enfonce les mains.
+narrateur|Le sable est froid au fond.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1718,7 +1780,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>Avant de partir, que fait-on ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1878,7 +1940,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>narrateur|Avant de partir, que fait-on ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1906,7 +1968,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : chercher seau et manteau ; les prendre. Sami respire. Sami retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+          <t>Oui. On va reprendre ses affaires, avant de partir. On cherche le seau et le manteau. On les prend. Bravo, Victorino. Tu as écouté. C'est du bon travail. Avant de partir. On continue ensemble ? Oui.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2050,7 +2112,16 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sami respire. Sami retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+          <t>narrateur|Oui.
+narrateur|On va reprendre ses affaires, avant de partir.
+narrateur|On cherche le seau et le manteau.
+narrateur|On les prend.
+maman|Bravo, Victorino.
+maman|Tu as écouté.
+papa|C'est du bon travail.
+enfant-m|Avant de partir.
+maman|On continue ensemble ?
+enfant-m|Oui.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2270,7 +2341,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi le ballon. Ça sent le pain chaud. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>Le ballon est près du bac. Il est un peu sablé, un peu lisse. Le ballon, Victorino. Le ballon. Victorino le fait rouler. Ça fait poum. On joue. Puis on reprend ses affaires. Avant de partir, on cherche. On prend le seau. On prend le manteau. Et le doudou. Oui. Les trois. Le ballon s'arrête contre le seau vert. Bravo. Tu t'en souviens.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2410,7 +2481,23 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi le ballon. Ça sent le pain chaud. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>narrateur|Le ballon est près du bac.
+narrateur|Il est un peu sablé, un peu lisse.
+papa|Le ballon, Victorino.
+enfant-m|Le ballon.
+narrateur|Victorino le fait rouler.
+narrateur|Ça fait poum.
+maman|On joue.
+maman|Puis on reprend ses affaires.
+papa|Avant de partir, on cherche.
+papa|On prend le seau.
+papa|On prend le manteau.
+enfant-m|Et le doudou.
+maman|Oui.
+maman|Les trois.
+narrateur|Le ballon s'arrête contre le seau vert.
+papa|Bravo.
+papa|Tu t'en souviens.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2438,7 +2525,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut aller vers le banc, le sac, ou le portail.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2606,7 +2693,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut aller vers le banc, le sac, ou le portail.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2634,7 +2721,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Tom. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent le bac à sable. Un grain de sable reste sur le seau. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le banc de bois est un peu chaud. Le manteau gris est plié dessus. Le manteau, Victorino. Il est au banc. Le manteau. Victorino le prend. Le tissu est doux. Maintenant le seau. Et le doudou. Victorino cherche. Il prend le seau. Il prend le doudou. Victorino a aussi le ballon sous le bras. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2774,10 +2861,37 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Tom. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|Ils quittent le bac à sable.
+narrateur|Un grain de sable reste sur le seau.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le banc de bois est un peu chaud.
+narrateur|Le manteau gris est plié dessus.
+papa|Le manteau, Victorino.
+papa|Il est au banc.
+enfant-m|Le manteau.
+narrateur|Victorino le prend.
+narrateur|Le tissu est doux.
+maman|Maintenant le seau.
+maman|Et le doudou.
+narrateur|Victorino cherche.
+narrateur|Il prend le seau.
+narrateur|Il prend le doudou.
+narrateur|Victorino a aussi le ballon sous le bras.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2802,7 +2916,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le banc est vide, maintenant. Le ballon tapote tout doux. Un grain de sable reste sur le rebord. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2942,7 +3056,14 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le banc est vide, maintenant.
+narrateur|Le ballon tapote tout doux.
+narrateur|Un grain de sable reste sur le rebord.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2970,7 +3091,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Léa. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent le bac à sable. Un grain de sable reste sur le seau. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le sac d'osier est près de l'herbe. Le seau vert l'attend, juste à côté. Le seau, Victorino. Près du sac. Le seau. Victorino le pose dans le sac. Maintenant le manteau. Et le doudou. Victorino cherche. Il prend le manteau. Il prend le doudou. Victorino a aussi le ballon sous le bras. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3110,10 +3231,36 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Léa. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr"/>
+          <t>narrateur|Ils quittent le bac à sable.
+narrateur|Un grain de sable reste sur le seau.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le sac d'osier est près de l'herbe.
+narrateur|Le seau vert l'attend, juste à côté.
+maman|Le seau, Victorino.
+maman|Près du sac.
+enfant-m|Le seau.
+narrateur|Victorino le pose dans le sac.
+papa|Maintenant le manteau.
+papa|Et le doudou.
+narrateur|Victorino cherche.
+narrateur|Il prend le manteau.
+narrateur|Il prend le doudou.
+narrateur|Victorino a aussi le ballon sous le bras.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3138,7 +3285,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le sac est un peu lourd. Le ballon tapote tout doux. Le banc n'a plus le manteau. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3278,7 +3425,14 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le sac est un peu lourd.
+narrateur|Le ballon tapote tout doux.
+narrateur|Le banc n'a plus le manteau.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3306,7 +3460,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Sami. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent le bac à sable. Un grain de sable reste sur le seau. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le portail du parc est un peu frais. Le doudou est assis contre le barreau. Le doudou, Victorino. Près du portail. Le doudou. Victorino le serre. On est près de partir. Maintenant le seau. Et le manteau. Victorino cherche. Il prend le seau. Il prend le manteau. Victorino a aussi le ballon sous le bras. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3446,10 +3600,37 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Sami. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+          <t>narrateur|Ils quittent le bac à sable.
+narrateur|Un grain de sable reste sur le seau.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le portail du parc est un peu frais.
+narrateur|Le doudou est assis contre le barreau.
+papa|Le doudou, Victorino.
+papa|Près du portail.
+enfant-m|Le doudou.
+narrateur|Victorino le serre.
+narrateur|On est près de partir.
+maman|Maintenant le seau.
+maman|Et le manteau.
+narrateur|Victorino cherche.
+narrateur|Il prend le seau.
+narrateur|Il prend le manteau.
+narrateur|Victorino a aussi le ballon sous le bras.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3474,7 +3655,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le portail reste ouvert un moment. Le ballon tapote tout doux. La fenêtre de la chambre attend. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3614,7 +3795,14 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le portail reste ouvert un moment.
+narrateur|Le ballon tapote tout doux.
+narrateur|La fenêtre de la chambre attend.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3642,7 +3830,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi le seau. Le vent est doux. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. papa n'est pas loin.</t>
+          <t>Le seau vert est dans le sable. Il a un grain collé au bord. Le seau, Victorino. Le seau. Victorino le soulève à deux mains. Ça fait un petit bruit de sable. On le reprend avant de partir. On cherche aussi le manteau. Il est au banc. Oui. On ira le prendre. Le seau tapote contre sa jambe. Bravo. Tu as le seau.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3782,7 +3970,20 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi le seau. Le vent est doux. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. papa n'est pas loin.</t>
+          <t>narrateur|Le seau vert est dans le sable.
+narrateur|Il a un grain collé au bord.
+maman|Le seau, Victorino.
+enfant-m|Le seau.
+narrateur|Victorino le soulève à deux mains.
+narrateur|Ça fait un petit bruit de sable.
+papa|On le reprend avant de partir.
+maman|On cherche aussi le manteau.
+enfant-m|Il est au banc.
+papa|Oui.
+papa|On ira le prendre.
+narrateur|Le seau tapote contre sa jambe.
+maman|Bravo.
+maman|Tu as le seau.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3810,7 +4011,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut aller vers le banc, le sac, ou le portail.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3978,7 +4179,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut aller vers le banc, le sac, ou le portail.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -4006,7 +4207,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Tom. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent le bac à sable. Un grain de sable reste sur le seau. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le banc de bois est un peu chaud. Le manteau gris est plié dessus. Le manteau, Victorino. Il est au banc. Le manteau. Victorino le prend. Le tissu est doux. Maintenant le seau. Et le doudou. Victorino cherche. Il prend le seau. Il prend le doudou. Le seau tapote déjà contre sa jambe. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4146,10 +4347,37 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Tom. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|Ils quittent le bac à sable.
+narrateur|Un grain de sable reste sur le seau.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le banc de bois est un peu chaud.
+narrateur|Le manteau gris est plié dessus.
+papa|Le manteau, Victorino.
+papa|Il est au banc.
+enfant-m|Le manteau.
+narrateur|Victorino le prend.
+narrateur|Le tissu est doux.
+maman|Maintenant le seau.
+maman|Et le doudou.
+narrateur|Victorino cherche.
+narrateur|Il prend le seau.
+narrateur|Il prend le doudou.
+narrateur|Le seau tapote déjà contre sa jambe.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4174,7 +4402,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le banc est vide, maintenant. Le seau vert sent encore le sable. L'oreille du doudou s'est dépliée un peu. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4314,7 +4542,14 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le banc est vide, maintenant.
+narrateur|Le seau vert sent encore le sable.
+narrateur|L'oreille du doudou s'est dépliée un peu.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4342,7 +4577,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Léa. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent le bac à sable. Un grain de sable reste sur le seau. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le sac d'osier est près de l'herbe. Le seau vert l'attend, juste à côté. Le seau, Victorino. Près du sac. Le seau. Victorino le pose dans le sac. Maintenant le manteau. Et le doudou. Victorino cherche. Il prend le manteau. Il prend le doudou. Le seau tapote déjà contre sa jambe. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4482,10 +4717,36 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Léa. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr"/>
+          <t>narrateur|Ils quittent le bac à sable.
+narrateur|Un grain de sable reste sur le seau.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le sac d'osier est près de l'herbe.
+narrateur|Le seau vert l'attend, juste à côté.
+maman|Le seau, Victorino.
+maman|Près du sac.
+enfant-m|Le seau.
+narrateur|Victorino le pose dans le sac.
+papa|Maintenant le manteau.
+papa|Et le doudou.
+narrateur|Victorino cherche.
+narrateur|Il prend le manteau.
+narrateur|Il prend le doudou.
+narrateur|Le seau tapote déjà contre sa jambe.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4510,7 +4771,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le sac est un peu lourd. Le seau vert sent encore le sable. Le toboggan ne fait plus de bruit. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4650,7 +4911,14 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le sac est un peu lourd.
+narrateur|Le seau vert sent encore le sable.
+narrateur|Le toboggan ne fait plus de bruit.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4678,7 +4946,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Sami. La lumière est claire. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent le bac à sable. Un grain de sable reste sur le seau. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le portail du parc est un peu frais. Le doudou est assis contre le barreau. Le doudou, Victorino. Près du portail. Le doudou. Victorino le serre. On est près de partir. Maintenant le seau. Et le manteau. Victorino cherche. Il prend le seau. Il prend le manteau. Le seau tapote déjà contre sa jambe. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4818,10 +5086,37 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Sami. La lumière est claire. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>narrateur|Ils quittent le bac à sable.
+narrateur|Un grain de sable reste sur le seau.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le portail du parc est un peu frais.
+narrateur|Le doudou est assis contre le barreau.
+papa|Le doudou, Victorino.
+papa|Près du portail.
+enfant-m|Le doudou.
+narrateur|Victorino le serre.
+narrateur|On est près de partir.
+maman|Maintenant le seau.
+maman|Et le manteau.
+narrateur|Victorino cherche.
+narrateur|Il prend le seau.
+narrateur|Il prend le manteau.
+narrateur|Le seau tapote déjà contre sa jambe.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4846,7 +5141,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le portail reste ouvert un moment. Le seau vert sent encore le sable. Une chaîne tinte, tout loin. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4986,7 +5281,14 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le portail reste ouvert un moment.
+narrateur|Le seau vert sent encore le sable.
+narrateur|Une chaîne tinte, tout loin.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5014,7 +5316,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi le doudou. Le sol est un peu froid. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. papa n'est pas loin.</t>
+          <t>Le doudou est assis au bord du bac. Il a du sable sur l'oreille. Le doudou, Victorino. Le doudou. Victorino le secoue, tout doux. On le reprend avant de partir. On cherche le seau. On cherche le manteau. Je les prends. Oui. On cherche. On prend. Le doudou sent encore le sable. Bravo. Tu t'en souviens. Ses affaires restent avec lui.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5154,7 +5456,22 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi le doudou. Le sol est un peu froid. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. papa n'est pas loin.</t>
+          <t>narrateur|Le doudou est assis au bord du bac.
+narrateur|Il a du sable sur l'oreille.
+papa|Le doudou, Victorino.
+enfant-m|Le doudou.
+narrateur|Victorino le secoue, tout doux.
+maman|On le reprend avant de partir.
+papa|On cherche le seau.
+papa|On cherche le manteau.
+enfant-m|Je les prends.
+maman|Oui.
+maman|On cherche.
+maman|On prend.
+narrateur|Le doudou sent encore le sable.
+papa|Bravo.
+papa|Tu t'en souviens.
+maman|Ses affaires restent avec lui.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5182,7 +5499,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut aller vers le banc, le sac, ou le portail.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5350,7 +5667,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut aller vers le banc, le sac, ou le portail.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5378,7 +5695,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Tom. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent le bac à sable. Un grain de sable reste sur le seau. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le banc de bois est un peu chaud. Le manteau gris est plié dessus. Le manteau, Victorino. Il est au banc. Le manteau. Victorino le prend. Le tissu est doux. Maintenant le seau. Et le doudou. Victorino cherche. Il prend le seau. Il prend le doudou. Le doudou est déjà contre lui. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5518,10 +5835,37 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Tom. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|Ils quittent le bac à sable.
+narrateur|Un grain de sable reste sur le seau.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le banc de bois est un peu chaud.
+narrateur|Le manteau gris est plié dessus.
+papa|Le manteau, Victorino.
+papa|Il est au banc.
+enfant-m|Le manteau.
+narrateur|Victorino le prend.
+narrateur|Le tissu est doux.
+maman|Maintenant le seau.
+maman|Et le doudou.
+narrateur|Victorino cherche.
+narrateur|Il prend le seau.
+narrateur|Il prend le doudou.
+narrateur|Le doudou est déjà contre lui.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5546,7 +5890,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le banc est vide, maintenant. Le doudou a l'oreille un peu pliée. Le sable du seau s'est calmé. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5686,7 +6030,14 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le banc est vide, maintenant.
+narrateur|Le doudou a l'oreille un peu pliée.
+narrateur|Le sable du seau s'est calmé.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5714,7 +6065,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Léa. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent le bac à sable. Un grain de sable reste sur le seau. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le sac d'osier est près de l'herbe. Le seau vert l'attend, juste à côté. Le seau, Victorino. Près du sac. Le seau. Victorino le pose dans le sac. Maintenant le manteau. Et le doudou. Victorino cherche. Il prend le manteau. Il prend le doudou. Le doudou est déjà contre lui. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5854,10 +6205,36 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Léa. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr"/>
+          <t>narrateur|Ils quittent le bac à sable.
+narrateur|Un grain de sable reste sur le seau.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le sac d'osier est près de l'herbe.
+narrateur|Le seau vert l'attend, juste à côté.
+maman|Le seau, Victorino.
+maman|Près du sac.
+enfant-m|Le seau.
+narrateur|Victorino le pose dans le sac.
+papa|Maintenant le manteau.
+papa|Et le doudou.
+narrateur|Victorino cherche.
+narrateur|Il prend le manteau.
+narrateur|Il prend le doudou.
+narrateur|Le doudou est déjà contre lui.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5882,7 +6259,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le sac est un peu lourd. Le doudou a l'oreille un peu pliée. Le portail se referme, tout doux. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6022,7 +6399,14 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le sac est un peu lourd.
+narrateur|Le doudou a l'oreille un peu pliée.
+narrateur|Le portail se referme, tout doux.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6050,7 +6434,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Sami. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent le bac à sable. Un grain de sable reste sur le seau. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le portail du parc est un peu frais. Le doudou est assis contre le barreau. Le doudou, Victorino. Près du portail. Le doudou. Victorino le serre. On est près de partir. Maintenant le seau. Et le manteau. Victorino cherche. Il prend le seau. Il prend le manteau. Le doudou est déjà contre lui. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6190,10 +6574,37 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Sami. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>narrateur|Ils quittent le bac à sable.
+narrateur|Un grain de sable reste sur le seau.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le portail du parc est un peu frais.
+narrateur|Le doudou est assis contre le barreau.
+papa|Le doudou, Victorino.
+papa|Près du portail.
+enfant-m|Le doudou.
+narrateur|Victorino le serre.
+narrateur|On est près de partir.
+maman|Maintenant le seau.
+maman|Et le manteau.
+narrateur|Victorino cherche.
+narrateur|Il prend le seau.
+narrateur|Il prend le manteau.
+narrateur|Le doudou est déjà contre lui.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6218,7 +6629,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le portail reste ouvert un moment. Le doudou a l'oreille un peu pliée. L'herbe a gardé une trace. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6358,7 +6769,14 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le portail reste ouvert un moment.
+narrateur|Le doudou a l'oreille un peu pliée.
+narrateur|L'herbe a gardé une trace.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6386,7 +6804,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers le toboggan. On entend un oiseau. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
+          <t>Victorino va vers le toboggan. Le métal est un peu chaud au soleil. Ça sent le fer, et l'herbe. Tu montes, tout doux. Wouush. Il glisse. Ses chaussures font toc. Le seau vert attend en bas. Le manteau gris est sur le banc. On joue. Après, on reprend ses affaires. Avant de partir. Je cherche. Je prends. Oui. Seau et manteau. Le doudou aussi. Victorino pose une main sur le rebord. Le métal est lisse.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6526,11 +6944,32 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Sami va vers le toboggan. On entend un oiseau. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On écoute jusqu'au bout.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Victorino va vers le toboggan.
+narrateur|Le métal est un peu chaud au soleil.
+narrateur|Ça sent le fer, et l'herbe.
+maman|Tu montes, tout doux.
+enfant-m|Wouush.
+narrateur|Il glisse.
+narrateur|Ses chaussures font toc.
+papa|Le seau vert attend en bas.
+papa|Le manteau gris est sur le banc.
+maman|On joue.
+maman|Après, on reprend ses affaires.
+maman|Avant de partir.
+enfant-m|Je cherche.
+enfant-m|Je prends.
+papa|Oui.
+papa|Seau et manteau.
+papa|Le doudou aussi.
+narrateur|Victorino pose une main sur le rebord.
+narrateur|Le métal est lisse.</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6555,7 +6994,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>On reprend ses affaires, avant de partir ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6715,7 +7154,7 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>narrateur|On reprend ses affaires, avant de partir ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6743,7 +7182,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : chercher seau et manteau ; les prendre. Sami respire. Sami retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+          <t>Oui. On va reprendre ses affaires, avant de partir. On cherche le seau et le manteau. On les prend. Bravo, Victorino. Tu as fait du bon travail. Le toboggan reste au parc. Mes affaires viennent. Oui. Avant de partir. On continue ? Oui.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6887,10 +7326,25 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sami respire. Sami retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr"/>
+          <t>narrateur|Oui.
+narrateur|On va reprendre ses affaires, avant de partir.
+narrateur|On cherche le seau et le manteau.
+narrateur|On les prend.
+papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Le toboggan reste au parc.
+enfant-m|Mes affaires viennent.
+papa|Oui.
+papa|Avant de partir.
+maman|On continue ?
+enfant-m|Oui.</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7107,7 +7561,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi le ballon. Une feuille tombe. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>Le ballon attend au pied du toboggan. Il est un peu chaud, un peu lisse. Le ballon, Victorino. Le ballon. Il rebondit une fois. Poum. On joue. Puis on reprend ses affaires. Avant de partir. On cherche le seau. On cherche le manteau. Je les prends. Bravo. Tu as écouté. Le ballon s'immobilise dans l'herbe. Il viendra avec nous.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7247,10 +7701,29 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi le ballon. Une feuille tombe. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Le ballon attend au pied du toboggan.
+narrateur|Il est un peu chaud, un peu lisse.
+maman|Le ballon, Victorino.
+enfant-m|Le ballon.
+narrateur|Il rebondit une fois.
+narrateur|Poum.
+papa|On joue.
+papa|Puis on reprend ses affaires.
+papa|Avant de partir.
+maman|On cherche le seau.
+maman|On cherche le manteau.
+enfant-m|Je les prends.
+papa|Bravo.
+papa|Tu as écouté.
+narrateur|Le ballon s'immobilise dans l'herbe.
+maman|Il viendra avec nous.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7275,7 +7748,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut aller vers le banc, le sac, ou le portail.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7443,7 +7916,7 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut aller vers le banc, le sac, ou le portail.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7471,7 +7944,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Tom. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent le toboggan. Le métal du toboggan est encore chaud. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le banc de bois est un peu chaud. Le manteau gris est plié dessus. Le manteau, Victorino. Il est au banc. Le manteau. Victorino le prend. Le tissu est doux. Maintenant le seau. Et le doudou. Victorino cherche. Il prend le seau. Il prend le doudou. Victorino a aussi le ballon sous le bras. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7611,10 +8084,37 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Tom. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|Ils quittent le toboggan.
+narrateur|Le métal du toboggan est encore chaud.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le banc de bois est un peu chaud.
+narrateur|Le manteau gris est plié dessus.
+papa|Le manteau, Victorino.
+papa|Il est au banc.
+enfant-m|Le manteau.
+narrateur|Victorino le prend.
+narrateur|Le tissu est doux.
+maman|Maintenant le seau.
+maman|Et le doudou.
+narrateur|Victorino cherche.
+narrateur|Il prend le seau.
+narrateur|Il prend le doudou.
+narrateur|Victorino a aussi le ballon sous le bras.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7639,7 +8139,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le banc est vide, maintenant. Le ballon tapote tout doux. Le ballon ne rebondit plus. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7779,7 +8279,14 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le banc est vide, maintenant.
+narrateur|Le ballon tapote tout doux.
+narrateur|Le ballon ne rebondit plus.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7807,7 +8314,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Léa. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent le toboggan. Le métal du toboggan est encore chaud. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le sac d'osier est près de l'herbe. Le seau vert l'attend, juste à côté. Le seau, Victorino. Près du sac. Le seau. Victorino le pose dans le sac. Maintenant le manteau. Et le doudou. Victorino cherche. Il prend le manteau. Il prend le doudou. Victorino a aussi le ballon sous le bras. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7947,10 +8454,36 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Léa. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr"/>
+          <t>narrateur|Ils quittent le toboggan.
+narrateur|Le métal du toboggan est encore chaud.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le sac d'osier est près de l'herbe.
+narrateur|Le seau vert l'attend, juste à côté.
+maman|Le seau, Victorino.
+maman|Près du sac.
+enfant-m|Le seau.
+narrateur|Victorino le pose dans le sac.
+papa|Maintenant le manteau.
+papa|Et le doudou.
+narrateur|Victorino cherche.
+narrateur|Il prend le manteau.
+narrateur|Il prend le doudou.
+narrateur|Victorino a aussi le ballon sous le bras.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7975,7 +8508,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le sac est un peu lourd. Le ballon tapote tout doux. Une feuille reste au fond du seau. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8115,7 +8648,14 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le sac est un peu lourd.
+narrateur|Le ballon tapote tout doux.
+narrateur|Une feuille reste au fond du seau.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8143,7 +8683,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Sami. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent le toboggan. Le métal du toboggan est encore chaud. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le portail du parc est un peu frais. Le doudou est assis contre le barreau. Le doudou, Victorino. Près du portail. Le doudou. Victorino le serre. On est près de partir. Maintenant le seau. Et le manteau. Victorino cherche. Il prend le seau. Il prend le manteau. Victorino a aussi le ballon sous le bras. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8283,10 +8823,37 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Sami. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr"/>
+          <t>narrateur|Ils quittent le toboggan.
+narrateur|Le métal du toboggan est encore chaud.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le portail du parc est un peu frais.
+narrateur|Le doudou est assis contre le barreau.
+papa|Le doudou, Victorino.
+papa|Près du portail.
+enfant-m|Le doudou.
+narrateur|Victorino le serre.
+narrateur|On est près de partir.
+maman|Maintenant le seau.
+maman|Et le manteau.
+narrateur|Victorino cherche.
+narrateur|Il prend le seau.
+narrateur|Il prend le manteau.
+narrateur|Victorino a aussi le ballon sous le bras.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8311,7 +8878,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le portail reste ouvert un moment. Le ballon tapote tout doux. Le métal du toboggan refroidit. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8451,7 +9018,14 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le portail reste ouvert un moment.
+narrateur|Le ballon tapote tout doux.
+narrateur|Le métal du toboggan refroidit.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8479,7 +9053,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi le seau. L'eau coule, tout petit bruit. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. papa n'est pas loin.</t>
+          <t>Le seau vert est au pied de l'échelle. Il y a une feuille dedans. Le seau, Victorino. Le seau. Victorino sort la feuille. Il la pose. On reprend le seau, avant de partir. Ensuite le manteau. Ensuite le doudou. Je cherche. Oui. On cherche. On prend. Le seau est un peu chaud au soleil. Bravo. Tu as le seau. Il tapote, tout doux.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8619,7 +9193,23 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi le seau. L'eau coule, tout petit bruit. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. papa n'est pas loin.</t>
+          <t>narrateur|Le seau vert est au pied de l'échelle.
+narrateur|Il y a une feuille dedans.
+papa|Le seau, Victorino.
+enfant-m|Le seau.
+narrateur|Victorino sort la feuille.
+narrateur|Il la pose.
+maman|On reprend le seau, avant de partir.
+papa|Ensuite le manteau.
+papa|Ensuite le doudou.
+enfant-m|Je cherche.
+maman|Oui.
+maman|On cherche.
+maman|On prend.
+narrateur|Le seau est un peu chaud au soleil.
+papa|Bravo.
+papa|Tu as le seau.
+maman|Il tapote, tout doux.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8647,7 +9237,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut aller vers le banc, le sac, ou le portail.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8815,7 +9405,7 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut aller vers le banc, le sac, ou le portail.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8843,7 +9433,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Tom. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent le toboggan. Le métal du toboggan est encore chaud. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le banc de bois est un peu chaud. Le manteau gris est plié dessus. Le manteau, Victorino. Il est au banc. Le manteau. Victorino le prend. Le tissu est doux. Maintenant le seau. Et le doudou. Victorino cherche. Il prend le seau. Il prend le doudou. Le seau tapote déjà contre sa jambe. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8983,10 +9573,37 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Tom. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|Ils quittent le toboggan.
+narrateur|Le métal du toboggan est encore chaud.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le banc de bois est un peu chaud.
+narrateur|Le manteau gris est plié dessus.
+papa|Le manteau, Victorino.
+papa|Il est au banc.
+enfant-m|Le manteau.
+narrateur|Victorino le prend.
+narrateur|Le tissu est doux.
+maman|Maintenant le seau.
+maman|Et le doudou.
+narrateur|Victorino cherche.
+narrateur|Il prend le seau.
+narrateur|Il prend le doudou.
+narrateur|Le seau tapote déjà contre sa jambe.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9011,7 +9628,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le banc est vide, maintenant. Le seau vert sent encore le sable. Le caillou est resté au parc. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9151,7 +9768,14 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le banc est vide, maintenant.
+narrateur|Le seau vert sent encore le sable.
+narrateur|Le caillou est resté au parc.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9179,7 +9803,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Léa. La lumière est claire. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent le toboggan. Le métal du toboggan est encore chaud. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le sac d'osier est près de l'herbe. Le seau vert l'attend, juste à côté. Le seau, Victorino. Près du sac. Le seau. Victorino le pose dans le sac. Maintenant le manteau. Et le doudou. Victorino cherche. Il prend le manteau. Il prend le doudou. Le seau tapote déjà contre sa jambe. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9319,10 +9943,36 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Léa. La lumière est claire. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr"/>
+          <t>narrateur|Ils quittent le toboggan.
+narrateur|Le métal du toboggan est encore chaud.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le sac d'osier est près de l'herbe.
+narrateur|Le seau vert l'attend, juste à côté.
+maman|Le seau, Victorino.
+maman|Près du sac.
+enfant-m|Le seau.
+narrateur|Victorino le pose dans le sac.
+papa|Maintenant le manteau.
+papa|Et le doudou.
+narrateur|Victorino cherche.
+narrateur|Il prend le manteau.
+narrateur|Il prend le doudou.
+narrateur|Le seau tapote déjà contre sa jambe.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9347,7 +9997,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le sac est un peu lourd. Le seau vert sent encore le sable. Le sac d'osier frotte la jambe. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9487,7 +10137,14 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le sac est un peu lourd.
+narrateur|Le seau vert sent encore le sable.
+narrateur|Le sac d'osier frotte la jambe.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9515,7 +10172,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Sami. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent le toboggan. Le métal du toboggan est encore chaud. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le portail du parc est un peu frais. Le doudou est assis contre le barreau. Le doudou, Victorino. Près du portail. Le doudou. Victorino le serre. On est près de partir. Maintenant le seau. Et le manteau. Victorino cherche. Il prend le seau. Il prend le manteau. Le seau tapote déjà contre sa jambe. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9655,10 +10312,37 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Sami. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr"/>
+          <t>narrateur|Ils quittent le toboggan.
+narrateur|Le métal du toboggan est encore chaud.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le portail du parc est un peu frais.
+narrateur|Le doudou est assis contre le barreau.
+papa|Le doudou, Victorino.
+papa|Près du portail.
+enfant-m|Le doudou.
+narrateur|Victorino le serre.
+narrateur|On est près de partir.
+maman|Maintenant le seau.
+maman|Et le manteau.
+narrateur|Victorino cherche.
+narrateur|Il prend le seau.
+narrateur|Il prend le manteau.
+narrateur|Le seau tapote déjà contre sa jambe.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9683,7 +10367,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le portail reste ouvert un moment. Le seau vert sent encore le sable. Le siège de la balançoire est vide. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9823,7 +10507,14 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le portail reste ouvert un moment.
+narrateur|Le seau vert sent encore le sable.
+narrateur|Le siège de la balançoire est vide.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9851,7 +10542,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi le doudou. Un vélo passe au loin. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. papa n'est pas loin.</t>
+          <t>Le doudou est assis sur la première marche. Il regarde le toboggan. Le doudou, Victorino. Le doudou. Victorino le serre contre lui. On le reprend avant de partir. On cherche aussi le seau et le manteau. Ils sont là. Oui. On les prendra. Le doudou a une odeur d'herbe. Bravo. Tu t'en souviens. Ses affaires restent avec lui.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9991,10 +10682,27 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi le doudou. Un vélo passe au loin. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr"/>
+          <t>narrateur|Le doudou est assis sur la première marche.
+narrateur|Il regarde le toboggan.
+maman|Le doudou, Victorino.
+enfant-m|Le doudou.
+narrateur|Victorino le serre contre lui.
+papa|On le reprend avant de partir.
+maman|On cherche aussi le seau et le manteau.
+enfant-m|Ils sont là.
+papa|Oui.
+papa|On les prendra.
+narrateur|Le doudou a une odeur d'herbe.
+maman|Bravo.
+maman|Tu t'en souviens.
+papa|Ses affaires restent avec lui.</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10019,7 +10727,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut aller vers le banc, le sac, ou le portail.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10187,7 +10895,7 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut aller vers le banc, le sac, ou le portail.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10215,7 +10923,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Tom. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent le toboggan. Le métal du toboggan est encore chaud. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le banc de bois est un peu chaud. Le manteau gris est plié dessus. Le manteau, Victorino. Il est au banc. Le manteau. Victorino le prend. Le tissu est doux. Maintenant le seau. Et le doudou. Victorino cherche. Il prend le seau. Il prend le doudou. Le doudou est déjà contre lui. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10355,10 +11063,37 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Tom. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|Ils quittent le toboggan.
+narrateur|Le métal du toboggan est encore chaud.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le banc de bois est un peu chaud.
+narrateur|Le manteau gris est plié dessus.
+papa|Le manteau, Victorino.
+papa|Il est au banc.
+enfant-m|Le manteau.
+narrateur|Victorino le prend.
+narrateur|Le tissu est doux.
+maman|Maintenant le seau.
+maman|Et le doudou.
+narrateur|Victorino cherche.
+narrateur|Il prend le seau.
+narrateur|Il prend le doudou.
+narrateur|Le doudou est déjà contre lui.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10383,7 +11118,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le banc est vide, maintenant. Le doudou a l'oreille un peu pliée. La chaîne ne tinte plus. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10523,7 +11258,14 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le banc est vide, maintenant.
+narrateur|Le doudou a l'oreille un peu pliée.
+narrateur|La chaîne ne tinte plus.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10551,7 +11293,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Léa. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent le toboggan. Le métal du toboggan est encore chaud. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le sac d'osier est près de l'herbe. Le seau vert l'attend, juste à côté. Le seau, Victorino. Près du sac. Le seau. Victorino le pose dans le sac. Maintenant le manteau. Et le doudou. Victorino cherche. Il prend le manteau. Il prend le doudou. Le doudou est déjà contre lui. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10691,10 +11433,36 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Léa. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr"/>
+          <t>narrateur|Ils quittent le toboggan.
+narrateur|Le métal du toboggan est encore chaud.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le sac d'osier est près de l'herbe.
+narrateur|Le seau vert l'attend, juste à côté.
+maman|Le seau, Victorino.
+maman|Près du sac.
+enfant-m|Le seau.
+narrateur|Victorino le pose dans le sac.
+papa|Maintenant le manteau.
+papa|Et le doudou.
+narrateur|Victorino cherche.
+narrateur|Il prend le manteau.
+narrateur|Il prend le doudou.
+narrateur|Le doudou est déjà contre lui.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10719,7 +11487,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le sac est un peu lourd. Le doudou a l'oreille un peu pliée. Le plancher de la chambre sera tiède. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10859,7 +11627,14 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le sac est un peu lourd.
+narrateur|Le doudou a l'oreille un peu pliée.
+narrateur|Le plancher de la chambre sera tiède.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10887,7 +11662,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Sami. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent le toboggan. Le métal du toboggan est encore chaud. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le portail du parc est un peu frais. Le doudou est assis contre le barreau. Le doudou, Victorino. Près du portail. Le doudou. Victorino le serre. On est près de partir. Maintenant le seau. Et le manteau. Victorino cherche. Il prend le seau. Il prend le manteau. Le doudou est déjà contre lui. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11027,10 +11802,37 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Sami. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr"/>
+          <t>narrateur|Ils quittent le toboggan.
+narrateur|Le métal du toboggan est encore chaud.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le portail du parc est un peu frais.
+narrateur|Le doudou est assis contre le barreau.
+papa|Le doudou, Victorino.
+papa|Près du portail.
+enfant-m|Le doudou.
+narrateur|Victorino le serre.
+narrateur|On est près de partir.
+maman|Maintenant le seau.
+maman|Et le manteau.
+narrateur|Victorino cherche.
+narrateur|Il prend le seau.
+narrateur|Il prend le manteau.
+narrateur|Le doudou est déjà contre lui.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11055,7 +11857,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le portail reste ouvert un moment. Le doudou a l'oreille un peu pliée. Le rebord n'a plus de sable. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11195,7 +11997,14 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le portail reste ouvert un moment.
+narrateur|Le doudou a l'oreille un peu pliée.
+narrateur|Le rebord n'a plus de sable.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11223,7 +12032,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers les balançoires. Ça sent le pain chaud. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On attend son tour. Je suis là. On reste ensemble.</t>
+          <t>Victorino va vers les balançoires. La chaîne tinte. Ting, ting. Le siège est un peu chaud. Tu te tiens bien, Victorino. Je me tiens. L'air passe sur son visage. Le manteau gris est sur le banc. Le seau vert est près du sac. On joue. Après, on reprend ses affaires. Avant de partir. Chercher. Prendre. Oui. Seau et manteau. Le doudou aussi. La chaîne ralentit. Victorino pose un pied par terre.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11363,11 +12172,32 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Sami va vers les balançoires. Ça sent le pain chaud. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On attend son tour.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr"/>
+          <t>narrateur|Victorino va vers les balançoires.
+narrateur|La chaîne tinte.
+narrateur|Ting, ting.
+narrateur|Le siège est un peu chaud.
+papa|Tu te tiens bien, Victorino.
+enfant-m|Je me tiens.
+narrateur|L'air passe sur son visage.
+maman|Le manteau gris est sur le banc.
+maman|Le seau vert est près du sac.
+papa|On joue.
+papa|Après, on reprend ses affaires.
+papa|Avant de partir.
+enfant-m|Chercher.
+enfant-m|Prendre.
+maman|Oui.
+maman|Seau et manteau.
+maman|Le doudou aussi.
+narrateur|La chaîne ralentit.
+narrateur|Victorino pose un pied par terre.</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11392,7 +12222,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>On reprend quoi, avant de partir ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11552,7 +12382,7 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>narrateur|On reprend quoi, avant de partir ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11580,7 +12410,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : chercher seau et manteau ; les prendre. Sami respire. Sami retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+          <t>Oui. On va reprendre ses affaires, avant de partir. On cherche le seau et le manteau. On les prend. Bravo, Victorino. Tu as écouté. C'est du bon travail. Seau, manteau, doudou. Oui. Les trois. On continue ensemble ? Oui.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11724,7 +12554,18 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sami respire. Sami retient : reprendre ses affaires, avant de partir. On continue, avec maman.</t>
+          <t>narrateur|Oui.
+narrateur|On va reprendre ses affaires, avant de partir.
+narrateur|On cherche le seau et le manteau.
+narrateur|On les prend.
+maman|Bravo, Victorino.
+maman|Tu as écouté.
+papa|C'est du bon travail.
+enfant-m|Seau, manteau, doudou.
+papa|Oui.
+papa|Les trois.
+maman|On continue ensemble ?
+enfant-m|Oui.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11944,7 +12785,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi le ballon. La lumière est claire. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>Le ballon est sous la balançoire. Il est un peu dans l'herbe. Le ballon, Victorino. Le ballon. Victorino le ramasse. Il est un peu humide. On joue. Puis on reprend ses affaires. Avant de partir, on cherche. On prend le seau. On prend le manteau. Et le doudou. Oui. Bravo. La chaîne tinte encore, tout loin. Tu t'en souviens bien.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12084,10 +12925,29 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi le ballon. La lumière est claire. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On montre du doigt, sans courir. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Le ballon est sous la balançoire.
+narrateur|Il est un peu dans l'herbe.
+papa|Le ballon, Victorino.
+enfant-m|Le ballon.
+narrateur|Victorino le ramasse.
+narrateur|Il est un peu humide.
+maman|On joue.
+maman|Puis on reprend ses affaires.
+papa|Avant de partir, on cherche.
+maman|On prend le seau.
+maman|On prend le manteau.
+enfant-m|Et le doudou.
+papa|Oui.
+papa|Bravo.
+narrateur|La chaîne tinte encore, tout loin.
+maman|Tu t'en souviens bien.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12112,7 +12972,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut aller vers le banc, le sac, ou le portail.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12280,7 +13140,7 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut aller vers le banc, le sac, ou le portail.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12308,7 +13168,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Tom. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent les balançoires. La chaîne tinte une dernière fois. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le banc de bois est un peu chaud. Le manteau gris est plié dessus. Le manteau, Victorino. Il est au banc. Le manteau. Victorino le prend. Le tissu est doux. Maintenant le seau. Et le doudou. Victorino cherche. Il prend le seau. Il prend le doudou. Victorino a aussi le ballon sous le bras. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12448,10 +13308,37 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Tom. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|Ils quittent les balançoires.
+narrateur|La chaîne tinte une dernière fois.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le banc de bois est un peu chaud.
+narrateur|Le manteau gris est plié dessus.
+papa|Le manteau, Victorino.
+papa|Il est au banc.
+enfant-m|Le manteau.
+narrateur|Victorino le prend.
+narrateur|Le tissu est doux.
+maman|Maintenant le seau.
+maman|Et le doudou.
+narrateur|Victorino cherche.
+narrateur|Il prend le seau.
+narrateur|Il prend le doudou.
+narrateur|Victorino a aussi le ballon sous le bras.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12476,7 +13363,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le banc est vide, maintenant. Le ballon tapote tout doux. Une chaussette attend près du lit. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12616,7 +13503,14 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le banc est vide, maintenant.
+narrateur|Le ballon tapote tout doux.
+narrateur|Une chaussette attend près du lit.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12644,7 +13538,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Léa. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent les balançoires. La chaîne tinte une dernière fois. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le sac d'osier est près de l'herbe. Le seau vert l'attend, juste à côté. Le seau, Victorino. Près du sac. Le seau. Victorino le pose dans le sac. Maintenant le manteau. Et le doudou. Victorino cherche. Il prend le manteau. Il prend le doudou. Victorino a aussi le ballon sous le bras. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12784,10 +13678,36 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Léa. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr"/>
+          <t>narrateur|Ils quittent les balançoires.
+narrateur|La chaîne tinte une dernière fois.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le sac d'osier est près de l'herbe.
+narrateur|Le seau vert l'attend, juste à côté.
+maman|Le seau, Victorino.
+maman|Près du sac.
+enfant-m|Le seau.
+narrateur|Victorino le pose dans le sac.
+papa|Maintenant le manteau.
+papa|Et le doudou.
+narrateur|Victorino cherche.
+narrateur|Il prend le manteau.
+narrateur|Il prend le doudou.
+narrateur|Victorino a aussi le ballon sous le bras.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12812,7 +13732,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le sac est un peu lourd. Le ballon tapote tout doux. Le manteau gris sent l'herbe. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12952,7 +13872,14 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le sac est un peu lourd.
+narrateur|Le ballon tapote tout doux.
+narrateur|Le manteau gris sent l'herbe.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12980,7 +13907,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Sami. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent les balançoires. La chaîne tinte une dernière fois. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le portail du parc est un peu frais. Le doudou est assis contre le barreau. Le doudou, Victorino. Près du portail. Le doudou. Victorino le serre. On est près de partir. Maintenant le seau. Et le manteau. Victorino cherche. Il prend le seau. Il prend le manteau. Victorino a aussi le ballon sous le bras. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13120,10 +14047,37 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Sami. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr"/>
+          <t>narrateur|Ils quittent les balançoires.
+narrateur|La chaîne tinte une dernière fois.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le portail du parc est un peu frais.
+narrateur|Le doudou est assis contre le barreau.
+papa|Le doudou, Victorino.
+papa|Près du portail.
+enfant-m|Le doudou.
+narrateur|Victorino le serre.
+narrateur|On est près de partir.
+maman|Maintenant le seau.
+maman|Et le manteau.
+narrateur|Victorino cherche.
+narrateur|Il prend le seau.
+narrateur|Il prend le manteau.
+narrateur|Victorino a aussi le ballon sous le bras.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13148,7 +14102,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le portail reste ouvert un moment. Le ballon tapote tout doux. Le seau vert a un peu de sable. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13288,7 +14242,14 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le portail reste ouvert un moment.
+narrateur|Le ballon tapote tout doux.
+narrateur|Le seau vert a un peu de sable.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13316,7 +14277,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi le seau. Il y a des miettes sur la table. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. papa n'est pas loin.</t>
+          <t>Le seau vert est près du poteau. Il y a un caillou dedans. Le seau, Victorino. Le seau. Victorino sort le caillou. Il le pose. On reprend le seau, avant de partir. On cherche le manteau. On cherche le doudou. Je les prends. Oui. On cherche. On prend. Le seau sent l'herbe coupée. Bravo. Tu as le seau. Il vient avec nous.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13456,7 +14417,23 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi le seau. Il y a des miettes sur la table. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. papa n'est pas loin.</t>
+          <t>narrateur|Le seau vert est près du poteau.
+narrateur|Il y a un caillou dedans.
+maman|Le seau, Victorino.
+enfant-m|Le seau.
+narrateur|Victorino sort le caillou.
+narrateur|Il le pose.
+papa|On reprend le seau, avant de partir.
+maman|On cherche le manteau.
+maman|On cherche le doudou.
+enfant-m|Je les prends.
+papa|Oui.
+papa|On cherche.
+papa|On prend.
+narrateur|Le seau sent l'herbe coupée.
+maman|Bravo.
+maman|Tu as le seau.
+papa|Il vient avec nous.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13484,7 +14461,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut aller vers le banc, le sac, ou le portail.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13652,7 +14629,7 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut aller vers le banc, le sac, ou le portail.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13680,7 +14657,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Tom. La lumière est claire. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent les balançoires. La chaîne tinte une dernière fois. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le banc de bois est un peu chaud. Le manteau gris est plié dessus. Le manteau, Victorino. Il est au banc. Le manteau. Victorino le prend. Le tissu est doux. Maintenant le seau. Et le doudou. Victorino cherche. Il prend le seau. Il prend le doudou. Le seau tapote déjà contre sa jambe. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13820,10 +14797,37 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Tom. La lumière est claire. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|Ils quittent les balançoires.
+narrateur|La chaîne tinte une dernière fois.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le banc de bois est un peu chaud.
+narrateur|Le manteau gris est plié dessus.
+papa|Le manteau, Victorino.
+papa|Il est au banc.
+enfant-m|Le manteau.
+narrateur|Victorino le prend.
+narrateur|Le tissu est doux.
+maman|Maintenant le seau.
+maman|Et le doudou.
+narrateur|Victorino cherche.
+narrateur|Il prend le seau.
+narrateur|Il prend le doudou.
+narrateur|Le seau tapote déjà contre sa jambe.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13848,7 +14852,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le banc est vide, maintenant. Le seau vert sent encore le sable. Le doudou a chaud contre lui. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13988,7 +14992,14 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le banc est vide, maintenant.
+narrateur|Le seau vert sent encore le sable.
+narrateur|Le doudou a chaud contre lui.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14016,7 +15027,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Léa. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent les balançoires. La chaîne tinte une dernière fois. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le sac d'osier est près de l'herbe. Le seau vert l'attend, juste à côté. Le seau, Victorino. Près du sac. Le seau. Victorino le pose dans le sac. Maintenant le manteau. Et le doudou. Victorino cherche. Il prend le manteau. Il prend le doudou. Le seau tapote déjà contre sa jambe. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14156,10 +15167,36 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Léa. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr"/>
+          <t>narrateur|Ils quittent les balançoires.
+narrateur|La chaîne tinte une dernière fois.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le sac d'osier est près de l'herbe.
+narrateur|Le seau vert l'attend, juste à côté.
+maman|Le seau, Victorino.
+maman|Près du sac.
+enfant-m|Le seau.
+narrateur|Victorino le pose dans le sac.
+papa|Maintenant le manteau.
+papa|Et le doudou.
+narrateur|Victorino cherche.
+narrateur|Il prend le manteau.
+narrateur|Il prend le doudou.
+narrateur|Le seau tapote déjà contre sa jambe.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14184,7 +15221,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le sac est un peu lourd. Le seau vert sent encore le sable. La première marche est vide. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14324,7 +15361,14 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le sac est un peu lourd.
+narrateur|Le seau vert sent encore le sable.
+narrateur|La première marche est vide.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14352,7 +15396,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Sami. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent les balançoires. La chaîne tinte une dernière fois. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le portail du parc est un peu frais. Le doudou est assis contre le barreau. Le doudou, Victorino. Près du portail. Le doudou. Victorino le serre. On est près de partir. Maintenant le seau. Et le manteau. Victorino cherche. Il prend le seau. Il prend le manteau. Le seau tapote déjà contre sa jambe. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14492,10 +15536,37 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Sami. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr"/>
+          <t>narrateur|Ils quittent les balançoires.
+narrateur|La chaîne tinte une dernière fois.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le portail du parc est un peu frais.
+narrateur|Le doudou est assis contre le barreau.
+papa|Le doudou, Victorino.
+papa|Près du portail.
+enfant-m|Le doudou.
+narrateur|Victorino le serre.
+narrateur|On est près de partir.
+maman|Maintenant le seau.
+maman|Et le manteau.
+narrateur|Victorino cherche.
+narrateur|Il prend le seau.
+narrateur|Il prend le manteau.
+narrateur|Le seau tapote déjà contre sa jambe.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14520,7 +15591,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le portail reste ouvert un moment. Le seau vert sent encore le sable. L'échelle du toboggan est calme. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14660,7 +15731,14 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le portail reste ouvert un moment.
+narrateur|Le seau vert sent encore le sable.
+narrateur|L'échelle du toboggan est calme.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14688,7 +15766,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi le doudou. Un chat miaule une fois. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. papa n'est pas loin.</t>
+          <t>Le doudou est sur le siège de la balançoire. Il se balance un tout petit peu. Le doudou, Victorino. Le doudou. Victorino le prend. L'oreille est pliée. On le reprend avant de partir. On cherche le seau. On cherche le manteau. Ils attendent. Oui. On ira les prendre. Le doudou est un peu chaud au soleil. Bravo. Tu t'en souviens. Ses affaires restent avec lui.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14828,10 +15906,29 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi le doudou. Un chat miaule une fois. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr"/>
+          <t>narrateur|Le doudou est sur le siège de la balançoire.
+narrateur|Il se balance un tout petit peu.
+papa|Le doudou, Victorino.
+enfant-m|Le doudou.
+narrateur|Victorino le prend.
+narrateur|L'oreille est pliée.
+maman|On le reprend avant de partir.
+papa|On cherche le seau.
+papa|On cherche le manteau.
+enfant-m|Ils attendent.
+maman|Oui.
+maman|On ira les prendre.
+narrateur|Le doudou est un peu chaud au soleil.
+papa|Bravo.
+papa|Tu t'en souviens.
+maman|Ses affaires restent avec lui.</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14856,7 +15953,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut aller vers le banc, le sac, ou le portail.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15024,7 +16121,7 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut aller vers le banc, le sac, ou le portail.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15052,7 +16149,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Tom. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent les balançoires. La chaîne tinte une dernière fois. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le banc de bois est un peu chaud. Le manteau gris est plié dessus. Le manteau, Victorino. Il est au banc. Le manteau. Victorino le prend. Le tissu est doux. Maintenant le seau. Et le doudou. Victorino cherche. Il prend le seau. Il prend le doudou. Le doudou est déjà contre lui. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15192,10 +16289,37 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Tom. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|Ils quittent les balançoires.
+narrateur|La chaîne tinte une dernière fois.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le banc de bois est un peu chaud.
+narrateur|Le manteau gris est plié dessus.
+papa|Le manteau, Victorino.
+papa|Il est au banc.
+enfant-m|Le manteau.
+narrateur|Victorino le prend.
+narrateur|Le tissu est doux.
+maman|Maintenant le seau.
+maman|Et le doudou.
+narrateur|Victorino cherche.
+narrateur|Il prend le seau.
+narrateur|Il prend le doudou.
+narrateur|Le doudou est déjà contre lui.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15220,7 +16344,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le banc est vide, maintenant. Le doudou a l'oreille un peu pliée. Le poteau n'a plus le seau. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15360,7 +16484,14 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le banc est vide, maintenant.
+narrateur|Le doudou a l'oreille un peu pliée.
+narrateur|Le poteau n'a plus le seau.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15388,7 +16519,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Léa. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent les balançoires. La chaîne tinte une dernière fois. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le sac d'osier est près de l'herbe. Le seau vert l'attend, juste à côté. Le seau, Victorino. Près du sac. Le seau. Victorino le pose dans le sac. Maintenant le manteau. Et le doudou. Victorino cherche. Il prend le manteau. Il prend le doudou. Le doudou est déjà contre lui. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15528,10 +16659,36 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Léa. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr"/>
+          <t>narrateur|Ils quittent les balançoires.
+narrateur|La chaîne tinte une dernière fois.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le sac d'osier est près de l'herbe.
+narrateur|Le seau vert l'attend, juste à côté.
+maman|Le seau, Victorino.
+maman|Près du sac.
+enfant-m|Le seau.
+narrateur|Victorino le pose dans le sac.
+papa|Maintenant le manteau.
+papa|Et le doudou.
+narrateur|Victorino cherche.
+narrateur|Il prend le manteau.
+narrateur|Il prend le doudou.
+narrateur|Le doudou est déjà contre lui.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15556,7 +16713,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le sac est un peu lourd. Le doudou a l'oreille un peu pliée. Le barreau du portail est froid. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15696,7 +16853,14 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le sac est un peu lourd.
+narrateur|Le doudou a l'oreille un peu pliée.
+narrateur|Le barreau du portail est froid.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15724,7 +16888,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Sami. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
+          <t>Ils quittent les balançoires. La chaîne tinte une dernière fois. C'est l'heure. On va reprendre ses affaires. Avant de partir. Le portail du parc est un peu frais. Le doudou est assis contre le barreau. Le doudou, Victorino. Près du portail. Le doudou. Victorino le serre. On est près de partir. Maintenant le seau. Et le manteau. Victorino cherche. Il prend le seau. Il prend le manteau. Le doudou est déjà contre lui. J'ai tout. Seau, manteau, doudou. Bravo. Tu as repris tes affaires. Avant de partir. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15864,10 +17028,37 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Sami. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr"/>
+          <t>narrateur|Ils quittent les balançoires.
+narrateur|La chaîne tinte une dernière fois.
+maman|C'est l'heure.
+maman|On va reprendre ses affaires.
+papa|Avant de partir.
+narrateur|Le portail du parc est un peu frais.
+narrateur|Le doudou est assis contre le barreau.
+papa|Le doudou, Victorino.
+papa|Près du portail.
+enfant-m|Le doudou.
+narrateur|Victorino le serre.
+narrateur|On est près de partir.
+maman|Maintenant le seau.
+maman|Et le manteau.
+narrateur|Victorino cherche.
+narrateur|Il prend le seau.
+narrateur|Il prend le manteau.
+narrateur|Le doudou est déjà contre lui.
+enfant-m|J'ai tout.
+maman|Seau, manteau, doudou.
+papa|Bravo.
+papa|Tu as repris tes affaires.
+papa|Avant de partir.
+narrateur|Ils marchent vers la maison.</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15892,7 +17083,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le portail reste ouvert un moment. Le doudou a l'oreille un peu pliée. L'oreiller attend le doudou. Bravo, Victorino. Tu as repris tes affaires, avant de partir. Merci. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16032,7 +17223,14 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le portail reste ouvert un moment.
+narrateur|Le doudou a l'oreille un peu pliée.
+narrateur|L'oreiller attend le doudou.
+maman|Bravo, Victorino.
+papa|Tu as repris tes affaires, avant de partir.
+enfant-m|Merci.
+maman|On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16054,7 +17252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16148,6 +17346,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>
